--- a/outputs/aasted3_run_comparison/summary/aasted3_zone_findings.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_zone_findings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone Findings" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zone Findings'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Zone Findings'!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1020,52 +1020,146 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>demoulding</t>
+          <t>demoulding_twisting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Demoulding zone / run end.</t>
+          <t>First demoulding subphase: acc z shifts from high plateau to low plateau while acc x shows a negative parabolic movement.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>similar length</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>accz_mean, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.03025716145833357</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>T7 (0.68 C abs mean delta)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5353190104166667</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>similar mean product temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>demoulding_vibration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Second demoulding subphase: vibration/shaking visible in acc z, acc x/y, and gyro y.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>48</v>
+      </c>
+      <c r="D14" t="n">
+        <v>42</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>shorter after alignment</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>T8_mean_C, T8_min_C, accz_mean, accz_std_median, gyroy_min, gyroy_max, gyroy_std_max</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>-10.61587112910068</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>T2 (11.20 C abs mean delta)</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.8395322221436651</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>T8_mean_C, T8_min_C, accz_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>-13.645263671875</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>T2 (14.48 C abs mean delta)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.277164713541667</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>final_demoulding</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Final demoulding/run-out after twisting and vibration.</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shorter after alignment</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_median, gyroy_std_max</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>-14.56825086805556</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>T2 (15.41 C abs mean delta)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.2783203125</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>comparison cooler than reference</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/aasted3_run_comparison/summary/aasted3_zone_findings.xlsx
+++ b/outputs/aasted3_run_comparison/summary/aasted3_zone_findings.xlsx
@@ -435,10 +435,10 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
@@ -515,35 +515,35 @@
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>slightly longer</t>
+          <t>similar length</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, accz_min, accz_max, accz_std_max, gyroy_mean, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>T8_mean_C, T8_min_C, T8_max_C, gyroy_max, gyroy_std_median</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7.566635653409092</v>
+        <v>-4.177369502314814</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>T5 (8.25 C abs mean delta)</t>
+          <t>T2 (5.00 C abs mean delta)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-0.06296756628787881</v>
+        <v>-0.4070891203703704</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>comparison warmer than reference</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -562,35 +562,35 @@
         <v>160</v>
       </c>
       <c r="D3" t="n">
-        <v>421</v>
+        <v>159</v>
       </c>
       <c r="E3" t="n">
-        <v>261</v>
+        <v>-1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>main stretched section</t>
+          <t>similar length</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, accz_min, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>T8_mean_C, T8_min_C, gyroy_min</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.86879969592343</v>
+        <v>-2.887585449218751</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>T3 (3.63 C abs mean delta)</t>
+          <t>T2 (3.56 C abs mean delta)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-0.1948500791432168</v>
+        <v>0.4154588916633702</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>comparison warmer than reference</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -621,23 +621,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>gyroy_mean, gyroy_min, gyroy_max</t>
+          <t>gyroy_std_median</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.6903826678240741</v>
+        <v>-1.030312039667508</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>T3 (2.01 C abs mean delta)</t>
+          <t>T2 (1.35 C abs mean delta)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-0.1419451678240742</v>
+        <v>0.3218736847643098</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>comparison warmer than reference</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -656,10 +656,10 @@
         <v>154</v>
       </c>
       <c r="D5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -668,23 +668,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>accz_min, gyroy_min, gyroy_std_max</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5000688604428355</v>
+        <v>-0.5537591314935071</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>T3 (1.12 C abs mean delta)</t>
+          <t>T2 (0.72 C abs mean delta)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.4424574528954652</v>
+        <v>0.1051643668831169</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>comparison warmer than reference</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -703,10 +703,10 @@
         <v>52</v>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -715,19 +715,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>accz_std_max, gyroy_min, gyroy_std_median, gyroy_std_max</t>
+          <t>gyroy_min, gyroy_std_max</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4807767427884613</v>
+        <v>-0.4508864182692314</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>T3 (1.25 C abs mean delta)</t>
+          <t>T7 (0.49 C abs mean delta)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-0.5907827524038463</v>
+        <v>-0.04852764423076938</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -750,10 +750,10 @@
         <v>84</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -762,23 +762,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_min</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.5268561492813582</v>
+        <v>-0.4333705357142854</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>T3 (0.87 C abs mean delta)</t>
+          <t>T7 (0.51 C abs mean delta)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-0.5254354266477933</v>
+        <v>-0.04280598958333348</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>comparison warmer than reference</t>
+          <t>similar mean product temperature</t>
         </is>
       </c>
     </row>
@@ -797,14 +797,14 @@
         <v>148</v>
       </c>
       <c r="D8" t="n">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>similar length</t>
+          <t>slightly longer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.287975084459459</v>
+        <v>-0.532161061010607</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>T5 (1.55 C abs mean delta)</t>
+          <t>T2 (0.62 C abs mean delta)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-0.4398886190878379</v>
+        <v>-0.1278374518671899</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>similar mean product temperature</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -844,31 +844,31 @@
         <v>142</v>
       </c>
       <c r="D9" t="n">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>90</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>similar length</t>
+          <t>main stretched section</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>T8_min_C, accz_std_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>accz_std_max, gyroy_std_max</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-0.1684953641687081</v>
+        <v>-0.4468607713088879</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>T5 (1.54 C abs mean delta)</t>
+          <t>T2 (0.53 C abs mean delta)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.4798336554654012</v>
+        <v>-0.06889271377185535</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -891,31 +891,31 @@
         <v>134</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>similar length</t>
+          <t>slightly longer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>T8_min_C, gyroy_min</t>
+          <t>T8_mean_C, T8_min_C, T8_max_C, gyroy_min, gyroy_std_max</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.1075776126469933</v>
+        <v>-0.2820732619073738</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>T5 (2.11 C abs mean delta)</t>
+          <t>T3 (0.37 C abs mean delta)</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.4000392656744687</v>
+        <v>-0.1478236117208076</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -938,31 +938,31 @@
         <v>606</v>
       </c>
       <c r="D11" t="n">
-        <v>611</v>
+        <v>674</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>similar length</t>
+          <t>main stretched section</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>no large zone-level IMU difference by this summary</t>
+          <t>T8_max_C</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1468137634075912</v>
+        <v>-0.42070367013287</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>T5 (1.45 C abs mean delta)</t>
+          <t>T7 (0.53 C abs mean delta)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.8706941006600659</v>
+        <v>-0.2477817587141689</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -985,35 +985,35 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>similar length</t>
+          <t>main stretched section</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>gyroy_std_median</t>
+          <t>accz_std_max, gyroy_min, gyroy_std_median</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.01797955377252265</v>
+        <v>-0.6616552501490464</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>T7 (0.69 C abs mean delta)</t>
+          <t>T2 (0.78 C abs mean delta)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.7195280827702701</v>
+        <v>-0.2084751341414945</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>similar mean product temperature</t>
+          <t>comparison cooler than reference</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1032,10 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1044,19 +1044,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>accz_mean, accz_std_max, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_max, gyroy_std_max</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.03025716145833357</v>
+        <v>-0.3234607514880946</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>T7 (0.68 C abs mean delta)</t>
+          <t>T2 (0.51 C abs mean delta)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.5353190104166667</v>
+        <v>-0.2910621279761905</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1079,35 +1079,35 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>shorter after alignment</t>
+          <t>similar length</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, accz_max, gyroy_min, gyroy_max, gyroy_std_max</t>
+          <t>gyroy_min</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-13.645263671875</v>
+        <v>-0.2389843749999997</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>T2 (14.48 C abs mean delta)</t>
+          <t>T2 (0.46 C abs mean delta)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-1.277164713541667</v>
+        <v>-0.2912565104166667</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>comparison cooler than reference</t>
+          <t>similar mean product temperature</t>
         </is>
       </c>
     </row>
@@ -1126,35 +1126,35 @@
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>shorter after alignment</t>
+          <t>slightly longer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>T8_mean_C, T8_min_C, T8_max_C, accz_mean, gyroy_mean, gyroy_min, gyroy_max, gyroy_std_median, gyroy_std_max</t>
+          <t>gyroy_mean, gyroy_min, gyroy_std_median</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-14.56825086805556</v>
+        <v>-0.1560036254084974</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>T2 (15.41 C abs mean delta)</t>
+          <t>T2 (0.39 C abs mean delta)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-1.2783203125</v>
+        <v>-0.3039981617647058</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>comparison cooler than reference</t>
+          <t>similar mean product temperature</t>
         </is>
       </c>
     </row>
